--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743269</v>
+        <v>122743270</v>
       </c>
       <c r="B2" t="n">
-        <v>90787</v>
+        <v>78796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672823</v>
+        <v>672786</v>
       </c>
       <c r="R2" t="n">
-        <v>7090829</v>
+        <v>7090833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743270</v>
+        <v>122743268</v>
       </c>
       <c r="B3" t="n">
-        <v>78694</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672786</v>
+        <v>672813</v>
       </c>
       <c r="R3" t="n">
-        <v>7090833</v>
+        <v>7090807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743268</v>
+        <v>122743269</v>
       </c>
       <c r="B4" t="n">
-        <v>74761</v>
+        <v>90890</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672813</v>
+        <v>672823</v>
       </c>
       <c r="R4" t="n">
-        <v>7090807</v>
+        <v>7090829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743270</v>
+        <v>122743269</v>
       </c>
       <c r="B2" t="n">
-        <v>78796</v>
+        <v>90894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672786</v>
+        <v>672823</v>
       </c>
       <c r="R2" t="n">
-        <v>7090833</v>
+        <v>7090829</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743268</v>
+        <v>122743270</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>78800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672813</v>
+        <v>672786</v>
       </c>
       <c r="R3" t="n">
-        <v>7090807</v>
+        <v>7090833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743269</v>
+        <v>122743268</v>
       </c>
       <c r="B4" t="n">
-        <v>90890</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672823</v>
+        <v>672813</v>
       </c>
       <c r="R4" t="n">
-        <v>7090829</v>
+        <v>7090807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743270</v>
+        <v>122743268</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672786</v>
+        <v>672813</v>
       </c>
       <c r="R3" t="n">
-        <v>7090833</v>
+        <v>7090807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743268</v>
+        <v>122743270</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>78800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672813</v>
+        <v>672786</v>
       </c>
       <c r="R4" t="n">
-        <v>7090807</v>
+        <v>7090833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743269</v>
+        <v>122743268</v>
       </c>
       <c r="B2" t="n">
-        <v>90894</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672823</v>
+        <v>672813</v>
       </c>
       <c r="R2" t="n">
-        <v>7090829</v>
+        <v>7090807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743268</v>
+        <v>122743269</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90894</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672813</v>
+        <v>672823</v>
       </c>
       <c r="R3" t="n">
-        <v>7090807</v>
+        <v>7090829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743268</v>
+        <v>122743270</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672813</v>
+        <v>672786</v>
       </c>
       <c r="R2" t="n">
-        <v>7090807</v>
+        <v>7090833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122743269</v>
       </c>
       <c r="B3" t="n">
-        <v>90894</v>
+        <v>90902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743270</v>
+        <v>122743268</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672786</v>
+        <v>672813</v>
       </c>
       <c r="R4" t="n">
-        <v>7090833</v>
+        <v>7090807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743270</v>
+        <v>122743269</v>
       </c>
       <c r="B2" t="n">
-        <v>78800</v>
+        <v>90902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672786</v>
+        <v>672823</v>
       </c>
       <c r="R2" t="n">
-        <v>7090833</v>
+        <v>7090829</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743269</v>
+        <v>122743268</v>
       </c>
       <c r="B3" t="n">
-        <v>90902</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672823</v>
+        <v>672813</v>
       </c>
       <c r="R3" t="n">
-        <v>7090829</v>
+        <v>7090807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743268</v>
+        <v>122743270</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>78798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672813</v>
+        <v>672786</v>
       </c>
       <c r="R4" t="n">
-        <v>7090807</v>
+        <v>7090833</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743269</v>
+        <v>122743270</v>
       </c>
       <c r="B2" t="n">
-        <v>90902</v>
+        <v>78798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672823</v>
+        <v>672786</v>
       </c>
       <c r="R2" t="n">
-        <v>7090829</v>
+        <v>7090833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743268</v>
+        <v>122743269</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672813</v>
+        <v>672823</v>
       </c>
       <c r="R3" t="n">
-        <v>7090807</v>
+        <v>7090829</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743270</v>
+        <v>122743268</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672786</v>
+        <v>672813</v>
       </c>
       <c r="R4" t="n">
-        <v>7090833</v>
+        <v>7090807</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743270</v>
+        <v>122743268</v>
       </c>
       <c r="B2" t="n">
-        <v>78798</v>
+        <v>74866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672786</v>
+        <v>672813</v>
       </c>
       <c r="R2" t="n">
-        <v>7090833</v>
+        <v>7090807</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743269</v>
+        <v>122743270</v>
       </c>
       <c r="B3" t="n">
-        <v>90902</v>
+        <v>78801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672823</v>
+        <v>672786</v>
       </c>
       <c r="R3" t="n">
-        <v>7090829</v>
+        <v>7090833</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743268</v>
+        <v>122743269</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>90905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672813</v>
+        <v>672823</v>
       </c>
       <c r="R4" t="n">
-        <v>7090807</v>
+        <v>7090829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743268</v>
+        <v>122743270</v>
       </c>
       <c r="B2" t="n">
-        <v>74866</v>
+        <v>78803</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672813</v>
+        <v>672786</v>
       </c>
       <c r="R2" t="n">
-        <v>7090807</v>
+        <v>7090833</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743270</v>
+        <v>122743268</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>74866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672786</v>
+        <v>672813</v>
       </c>
       <c r="R3" t="n">
-        <v>7090833</v>
+        <v>7090807</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122743269</v>
       </c>
       <c r="B4" t="n">
-        <v>90905</v>
+        <v>90907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 33729-2020 artfynd.xlsx
+++ b/artfynd/A 33729-2020 artfynd.xlsx
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918815</v>
+        <v>126912928</v>
       </c>
       <c r="B5" t="n">
-        <v>78738</v>
+        <v>92609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672767</v>
+        <v>672944</v>
       </c>
       <c r="R5" t="n">
-        <v>7090991</v>
+        <v>7090839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,26 +1078,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126912889</v>
+        <v>126918815</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672798</v>
+        <v>672767</v>
       </c>
       <c r="R6" t="n">
-        <v>7091015</v>
+        <v>7090991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,22 +1175,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126918830</v>
+        <v>126912889</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672770</v>
+        <v>672798</v>
       </c>
       <c r="R7" t="n">
-        <v>7090981</v>
+        <v>7091015</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,48 +1276,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126912928</v>
+        <v>126918830</v>
       </c>
       <c r="B8" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672944</v>
+        <v>672770</v>
       </c>
       <c r="R8" t="n">
-        <v>7090839</v>
+        <v>7090981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,22 +1373,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919058</v>
+        <v>126912873</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672737</v>
+        <v>672756</v>
       </c>
       <c r="R9" t="n">
-        <v>7091090</v>
+        <v>7091126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,26 +1474,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912873</v>
+        <v>126919058</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672756</v>
+        <v>672737</v>
       </c>
       <c r="R10" t="n">
-        <v>7091126</v>
+        <v>7091090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,44 +1571,48 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126912743</v>
+        <v>126912932</v>
       </c>
       <c r="B11" t="n">
-        <v>97239</v>
+        <v>78678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672864</v>
+        <v>672755</v>
       </c>
       <c r="R11" t="n">
-        <v>7090784</v>
+        <v>7091113</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,17 +1677,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918821</v>
+        <v>126912715</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1695,21 +1695,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672752</v>
+        <v>672914</v>
       </c>
       <c r="R12" t="n">
-        <v>7091197</v>
+        <v>7090807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,26 +1769,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126919053</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1889,7 +1885,7 @@
         <v>126919056</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,7 +1986,7 @@
         <v>126912875</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,10 +2080,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912932</v>
+        <v>126918821</v>
       </c>
       <c r="B16" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,21 +2091,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2115,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672755</v>
+        <v>672752</v>
       </c>
       <c r="R16" t="n">
-        <v>7091113</v>
+        <v>7091197</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,44 +2165,48 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912726</v>
+        <v>126912743</v>
       </c>
       <c r="B17" t="n">
-        <v>79569</v>
+        <v>97314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672750</v>
+        <v>672864</v>
       </c>
       <c r="R17" t="n">
-        <v>7091112</v>
+        <v>7090784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912715</v>
+        <v>126912726</v>
       </c>
       <c r="B18" t="n">
-        <v>79598</v>
+        <v>79600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672914</v>
+        <v>672750</v>
       </c>
       <c r="R18" t="n">
-        <v>7090807</v>
+        <v>7091112</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918827</v>
+        <v>126912903</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672753</v>
+        <v>672791</v>
       </c>
       <c r="R19" t="n">
-        <v>7091016</v>
+        <v>7090883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2460,26 +2460,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126912903</v>
+        <v>126918827</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672791</v>
+        <v>672753</v>
       </c>
       <c r="R20" t="n">
-        <v>7090883</v>
+        <v>7091016</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2561,22 +2557,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126912882</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         <v>126913219</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>126918828</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>126918825</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126912770</v>
+        <v>126912862</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672777</v>
+        <v>672787</v>
       </c>
       <c r="R25" t="n">
-        <v>7090805</v>
+        <v>7091154</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126912862</v>
+        <v>126912770</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672787</v>
+        <v>672777</v>
       </c>
       <c r="R26" t="n">
-        <v>7091154</v>
+        <v>7090805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
         <v>126913216</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>126919059</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912769</v>
+        <v>126912870</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672768</v>
+        <v>672767</v>
       </c>
       <c r="R29" t="n">
-        <v>7090779</v>
+        <v>7091137</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3469,7 +3469,7 @@
         <v>126912906</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,17 +3556,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912870</v>
+        <v>126912769</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672767</v>
+        <v>672768</v>
       </c>
       <c r="R31" t="n">
-        <v>7091137</v>
+        <v>7090779</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3653,17 +3653,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912860</v>
+        <v>126912771</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672791</v>
+        <v>672794</v>
       </c>
       <c r="R32" t="n">
-        <v>7091154</v>
+        <v>7090788</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3750,17 +3750,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126912771</v>
+        <v>126912860</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672794</v>
+        <v>672791</v>
       </c>
       <c r="R33" t="n">
-        <v>7090788</v>
+        <v>7091154</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
         <v>126918831</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>126912749</v>
       </c>
       <c r="B35" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>126912717</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>126912944</v>
       </c>
       <c r="B37" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912714</v>
+        <v>126912898</v>
       </c>
       <c r="B38" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4262,21 +4262,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672794</v>
+        <v>672804</v>
       </c>
       <c r="R38" t="n">
-        <v>7090788</v>
+        <v>7090880</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
         <v>126912910</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4438,17 +4438,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126912898</v>
+        <v>126912714</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4456,21 +4456,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672804</v>
+        <v>672794</v>
       </c>
       <c r="R40" t="n">
-        <v>7090880</v>
+        <v>7090788</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126912908</v>
+        <v>126913225</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4553,21 +4553,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672789</v>
+        <v>672822</v>
       </c>
       <c r="R41" t="n">
-        <v>7090875</v>
+        <v>7090825</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4627,22 +4627,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126918824</v>
+        <v>126912908</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4674,10 +4678,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672781</v>
+        <v>672789</v>
       </c>
       <c r="R42" t="n">
-        <v>7091162</v>
+        <v>7090875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4724,26 +4728,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126913225</v>
+        <v>126918824</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,21 +4751,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672822</v>
+        <v>672781</v>
       </c>
       <c r="R43" t="n">
-        <v>7090825</v>
+        <v>7091162</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,12 +4825,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4844,7 +4844,7 @@
         <v>126912776</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4941,7 +4941,7 @@
         <v>126912716</v>
       </c>
       <c r="B45" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919051</v>
+        <v>126919054</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672702</v>
+        <v>672705</v>
       </c>
       <c r="R46" t="n">
-        <v>7091061</v>
+        <v>7091127</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919054</v>
+        <v>126919057</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672705</v>
+        <v>672730</v>
       </c>
       <c r="R47" t="n">
-        <v>7091127</v>
+        <v>7091091</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5237,10 +5237,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126918826</v>
+        <v>126912877</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672744</v>
+        <v>672754</v>
       </c>
       <c r="R48" t="n">
-        <v>7091079</v>
+        <v>7091099</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5322,26 +5322,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912877</v>
+        <v>126918826</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5373,10 +5369,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672754</v>
+        <v>672744</v>
       </c>
       <c r="R49" t="n">
-        <v>7091099</v>
+        <v>7091079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5423,22 +5419,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>126912774</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5525,17 +5525,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919057</v>
+        <v>126919051</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672730</v>
+        <v>672702</v>
       </c>
       <c r="R51" t="n">
-        <v>7091091</v>
+        <v>7091061</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126912727</v>
+        <v>126912927</v>
       </c>
       <c r="B52" t="n">
-        <v>56849</v>
+        <v>92609</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5644,43 +5644,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672766</v>
+        <v>672768</v>
       </c>
       <c r="R52" t="n">
-        <v>7090783</v>
+        <v>7091045</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5732,39 +5723,39 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126912927</v>
+        <v>126918820</v>
       </c>
       <c r="B53" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5774,10 +5765,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672768</v>
+        <v>672755</v>
       </c>
       <c r="R53" t="n">
-        <v>7091045</v>
+        <v>7091121</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5824,22 +5815,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913218</v>
+        <v>126912887</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5871,10 +5866,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672656</v>
+        <v>672750</v>
       </c>
       <c r="R54" t="n">
-        <v>7091011</v>
+        <v>7091052</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,26 +5916,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126918820</v>
+        <v>126918832</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5972,10 +5963,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672755</v>
+        <v>672794</v>
       </c>
       <c r="R55" t="n">
-        <v>7091121</v>
+        <v>7090881</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6038,10 +6029,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126918832</v>
+        <v>126913218</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6073,10 +6064,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672794</v>
+        <v>672656</v>
       </c>
       <c r="R56" t="n">
-        <v>7090881</v>
+        <v>7091011</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6123,12 +6114,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6139,10 +6130,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912887</v>
+        <v>126912865</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6174,10 +6165,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672750</v>
+        <v>672783</v>
       </c>
       <c r="R57" t="n">
-        <v>7091052</v>
+        <v>7091147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6236,45 +6227,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912865</v>
+        <v>126912727</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672783</v>
+        <v>672766</v>
       </c>
       <c r="R58" t="n">
-        <v>7091147</v>
+        <v>7090783</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6434,10 +6434,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912901</v>
+        <v>126919050</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6469,10 +6469,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672805</v>
+        <v>672719</v>
       </c>
       <c r="R60" t="n">
-        <v>7090886</v>
+        <v>7091052</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6519,22 +6519,26 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126919050</v>
+        <v>126912901</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6566,10 +6570,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672719</v>
+        <v>672805</v>
       </c>
       <c r="R61" t="n">
-        <v>7091052</v>
+        <v>7090886</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6616,48 +6620,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B62" t="n">
-        <v>92535</v>
+        <v>91337</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R62" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6717,48 +6717,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B63" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6768,10 +6764,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R63" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6818,22 +6814,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6841,21 +6841,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R64" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6915,26 +6915,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126912762</v>
+        <v>126919049</v>
       </c>
       <c r="B65" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6942,21 +6938,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6966,10 +6962,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672743</v>
+        <v>672651</v>
       </c>
       <c r="R65" t="n">
-        <v>7091094</v>
+        <v>7091012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7016,22 +7012,26 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>126912773</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7118,17 +7118,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126912723</v>
+        <v>126919060</v>
       </c>
       <c r="B67" t="n">
-        <v>91167</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672755</v>
+        <v>672791</v>
       </c>
       <c r="R67" t="n">
-        <v>7091097</v>
+        <v>7091150</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7210,22 +7210,26 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
         <v>126912868</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7322,7 +7326,7 @@
         <v>126912879</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7416,10 +7420,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126919060</v>
+        <v>126912723</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>91241</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7427,21 +7431,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7451,10 +7455,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672791</v>
+        <v>672755</v>
       </c>
       <c r="R70" t="n">
-        <v>7091150</v>
+        <v>7091097</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7501,26 +7505,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126912884</v>
+        <v>126912772</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672746</v>
+        <v>672805</v>
       </c>
       <c r="R71" t="n">
-        <v>7091051</v>
+        <v>7090767</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7607,17 +7607,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126912754</v>
+        <v>126912892</v>
       </c>
       <c r="B72" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7625,21 +7625,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672757</v>
+        <v>672787</v>
       </c>
       <c r="R72" t="n">
-        <v>7090796</v>
+        <v>7090995</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7711,10 +7711,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126913217</v>
+        <v>126912754</v>
       </c>
       <c r="B73" t="n">
-        <v>79598</v>
+        <v>78769</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7722,21 +7722,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672643</v>
+        <v>672757</v>
       </c>
       <c r="R73" t="n">
-        <v>7091013</v>
+        <v>7090796</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7796,26 +7796,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126912892</v>
+        <v>126912884</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7847,10 +7843,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672787</v>
+        <v>672746</v>
       </c>
       <c r="R74" t="n">
-        <v>7090995</v>
+        <v>7091051</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7909,10 +7905,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126912772</v>
+        <v>126913217</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7920,21 +7916,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7944,10 +7940,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672805</v>
+        <v>672643</v>
       </c>
       <c r="R75" t="n">
-        <v>7090767</v>
+        <v>7091013</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7994,22 +7990,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
         <v>126917430</v>
       </c>
       <c r="B76" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>126917446</v>
       </c>
       <c r="B77" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>126917438</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>126917439</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>126917445</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>126917436</v>
       </c>
       <c r="B81" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>126917440</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8746,10 +8746,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B83" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8757,31 +8757,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8789,10 +8784,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R83" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8833,6 +8828,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8855,10 +8851,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8866,26 +8862,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -8893,10 +8894,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R84" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -8937,7 +8938,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>126917444</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>126917442</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9170,32 +9170,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>91580</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R87" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9275,32 +9275,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B88" t="n">
-        <v>91506</v>
+        <v>79011</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R88" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9493,7 +9493,7 @@
         <v>126913591</v>
       </c>
       <c r="B90" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9591,10 +9591,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B91" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9602,21 +9602,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R91" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9692,10 +9692,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9703,21 +9703,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9727,10 +9727,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R92" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9796,7 +9796,7 @@
         <v>126913587</v>
       </c>
       <c r="B93" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>126913589</v>
       </c>
       <c r="B94" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>126913588</v>
       </c>
       <c r="B95" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>126913582</v>
       </c>
       <c r="B96" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10197,10 +10197,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126913584</v>
+        <v>126913590</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10232,10 +10232,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>672813</v>
+        <v>672842</v>
       </c>
       <c r="R97" t="n">
-        <v>7091003</v>
+        <v>7090847</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126913590</v>
+        <v>126913584</v>
       </c>
       <c r="B98" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>672842</v>
+        <v>672813</v>
       </c>
       <c r="R98" t="n">
-        <v>7090847</v>
+        <v>7091003</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10402,7 +10402,7 @@
         <v>126913585</v>
       </c>
       <c r="B99" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>126913593</v>
       </c>
       <c r="B100" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
